--- a/1-LATEX/2-DADOS/3-OUTPUT/vies_publicacao.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/vies_publicacao.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -422,10 +422,10 @@
         <v>37</v>
       </c>
       <c r="E3">
-        <v>0.172859450726979</v>
+        <v>0.3823027085470957</v>
       </c>
       <c r="F3">
-        <v>0.1542711260589907</v>
+        <v>7.005550289505333E-06</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -443,10 +443,10 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>0.4847942754919499</v>
+        <v>0.1504132231404958</v>
       </c>
       <c r="F4">
-        <v>0.0001624347412385448</v>
+        <v>0.2245040050809938</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -464,10 +464,10 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0.1504132231404958</v>
+        <v>0.6340182908230633</v>
       </c>
       <c r="F5">
-        <v>0.2245040050809938</v>
+        <v>8.559274683161015E-07</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -485,10 +485,10 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0.6340182908230633</v>
+        <v>0.03795384705458192</v>
       </c>
       <c r="F6">
-        <v>8.559274683161015E-07</v>
+        <v>0.7578512227782557</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -503,15 +503,51 @@
         </is>
       </c>
       <c r="B7">
-        <v>37</v>
-      </c>
-      <c r="E7">
-        <v>0.03795384705458192</v>
-      </c>
-      <c r="F7">
-        <v>0.7578512227782557</v>
+        <v>47</v>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>-0.3432835820895522</v>
+      </c>
+      <c r="F8">
+        <v>0.01821368896097922</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>47</v>
+      </c>
+      <c r="E9">
+        <v>-0.2941176470588235</v>
+      </c>
+      <c r="F9">
+        <v>0.03152471506597961</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
